--- a/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_3/CF_M05_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,289 +471,625 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD02</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M05_C09 , *CF_M05_C11</t>
+          <t>CF_M05_C07 , *CF_M05_C10, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Integrity; Confidentiality</t>
+          <t>Capacity; Flexibility; Scalability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leader Microservice</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This microservice incorporates protection mechanisms to ensure the integrity and confidentiality of communications, blocking any unauthorized connection attempt and applying security protocols to prevent improper access and possible vulnerabilities.</t>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.7897</v>
+        <v>0.6499</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Integrity; Confidentiality</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Communication Log Microservice</t>
+          <t>Leader Microservice</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>This microservice incorporates protection mechanisms to ensure the integrity and confidentiality of communications, blocking any unauthorized connection attempt and applying security protocols to prevent improper access and possible vulnerabilities.</t>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.665</v>
+        <v>0.6165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>CF_M05_C01, *CF_M05_C12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Presentation and user experience</t>
+          <t>Appearance; Visual and Functional consistency</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8676</v>
+        <v>0.6375999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Capacity; Maintainability; Scalability</t>
+          <t>Confidentiality</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Access Control Microservice</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM pattern, as its architecture is based on components and services, which is designed for the implementation of user interfaces.</t>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.726</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Angular; Spring Boot</t>
+          <t>Communication Log Microservice</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated, clarifying roles, avoiding unnecessary coupling, and facilitating testing, reusing, and maintaining the code over time.</t>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7173</v>
+        <v>0.5933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Availability; Capacity; Access; Scalability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>*CF_M05_C15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>61</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Presentation and user experience</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA) [19] que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6637</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CF_M05_C09 , *CF_M05_C16, *CF_M05_C17</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>61</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Integrity; Security; Data persistence</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>76</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Capacity; Maintainability; Scalability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA) [19] que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Angular; Spring Boot</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA) [19] que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Availability; Capacity</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pel desplegament de l’aplicació s’ha fetús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s), una plataforma d’orquestració de contenidors creada per Google, sense necessitat d’instal·lar-la ni mantenir-la.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6837</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>78</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6222</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>CF_M05_AD13</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>*CF_M05_C18</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E14" t="n">
         <v>82</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Scalability</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.767</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AWS és una plataforma cloud consolidada amb serveis robustos i una infraestructura fiable. Un dels grans avantatges d’AWS és que disposa d’una selecció molt àmplia de serveis: des del desplegament de servidors i bases de dades, fins a IA, emmagatzematge, seguretat i serveis específics per sectors. Aquesta diversitat fa que sigui fàcil adaptar-se a les necessitats del projecte, permet créixer i escalar el projecte de manera àgil i elimina la necessitat de buscar altre plataformes quan els requisits evolucionen. Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura. Una altra raó per la qual es va triar AWS va ser que aquesta plataforma inverteix molt en seguretat i certificacions, gestiona múltiples nivells de seguretat i ofereix eines per protegir dades i infraestructures facilitant el compliment de normatives legals i estàndards internacionals.</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6818</v>
       </c>
     </row>
   </sheetData>
